--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519841.8155814523</v>
+        <v>519842</v>
       </c>
       <c r="R2" t="n">
-        <v>6328895.216399055</v>
+        <v>6328895</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,12 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519841.8155814523</v>
+        <v>519842</v>
       </c>
       <c r="R3" t="n">
-        <v>6328895.216399055</v>
+        <v>6328895</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -866,19 +846,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104061</v>
+        <v>104070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104070</v>
+        <v>104073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104100</v>
+        <v>104106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104106</v>
+        <v>104113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104117</v>
+        <v>104124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104127</v>
+        <v>104132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104132</v>
+        <v>104140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104140</v>
+        <v>104150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42930-2022 artfynd.xlsx
+++ b/artfynd/A 42930-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74149726</v>
       </c>
       <c r="B2" t="n">
-        <v>98589</v>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74464206</v>
       </c>
       <c r="B3" t="n">
-        <v>104150</v>
+        <v>104640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
